--- a/task132/target/protection_renewal_programme_2026.xlsx
+++ b/task132/target/protection_renewal_programme_2026.xlsx
@@ -2,7 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -12,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -487,12 +486,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TS-103</t>
+          <t>DS-001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Elm Mills</t>
+          <t>Cedar Road</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -502,7 +501,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -519,12 +518,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DS-055</t>
+          <t>DS-127</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ash Station</t>
+          <t>Kingsmount</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,7 +533,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 4 bays</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -551,12 +550,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TS-044</t>
+          <t>DS-080</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oak Station</t>
+          <t>Spring Ridge</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -566,7 +565,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (6) and RTU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -583,12 +582,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DS-031</t>
+          <t>TS-025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Juniper Lake</t>
+          <t>Brant Falls</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -598,7 +597,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (6 feeder bays)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -615,12 +614,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DS-135</t>
+          <t>TS-058</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aspen Creek</t>
+          <t>Elm Point</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -630,7 +629,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (1 bays)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -647,22 +646,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DS-121</t>
+          <t>DS-119</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alder Landing</t>
+          <t>Cedar Junction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (1 bays)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -679,12 +678,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DS-112</t>
+          <t>DS-014</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alder Creek</t>
+          <t>Cedarbrook</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -694,7 +693,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (2 feeder bays)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -711,22 +710,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DS-095</t>
+          <t>DS-054</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sumac Creek</t>
+          <t>Long River</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (4 feeder bays)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -743,22 +742,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DS-090</t>
+          <t>DS-134</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oak Hill</t>
+          <t>Mossfield</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 2 bays</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -775,22 +774,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DS-017</t>
+          <t>DS-046</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Birch Mills</t>
+          <t>Hawkford</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (3) and RTU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -807,22 +806,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DS-138</t>
+          <t>DS-120</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ash Bay</t>
+          <t>Lakewood</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 3 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -839,22 +838,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DS-021</t>
+          <t>DS-128</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sumac Mills</t>
+          <t>Rock Bay</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -871,12 +870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DS-059</t>
+          <t>DS-016</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spruce Ridge</t>
+          <t>Long Road</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -886,7 +885,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 2 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -903,22 +902,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DS-096</t>
+          <t>DS-002</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poplar Bay</t>
+          <t>West River</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (5) and RTU</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -935,22 +934,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DS-065</t>
+          <t>DS-064</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Maple Junction</t>
+          <t>Kettle Bridge</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (5) and RTU</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -967,22 +966,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DS-022</t>
+          <t>TS-110</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ashfield</t>
+          <t>Red Creek</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (7) and RTU</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -999,22 +998,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DS-091</t>
+          <t>DS-106</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pine Lake</t>
+          <t>Willow Bridge</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (9 feeder bays)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1031,22 +1030,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DS-106</t>
+          <t>DS-069</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spruce Creek</t>
+          <t>Sand Landing</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (6 feeder bays)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1063,12 +1062,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DS-132</t>
+          <t>DS-122</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pine Crossing</t>
+          <t>Ash Bridge</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1078,7 +1077,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 8 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1095,12 +1094,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DS-046</t>
+          <t>DS-033</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Willow Falls</t>
+          <t>Elmdale</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1110,7 +1109,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (4) and RTU</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1127,22 +1126,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DS-071</t>
+          <t>DS-075</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sumacwood</t>
+          <t>Ash Creek</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (1) and RTU</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1159,12 +1158,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DS-014</t>
+          <t>DS-104</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oak Landing</t>
+          <t>Stone Mills</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1174,7 +1173,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 6 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1191,22 +1190,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DS-114</t>
+          <t>TS-138</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tamarack Bay</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 8 bays</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1223,22 +1222,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DS-136</t>
+          <t>DS-028</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Beech Creek</t>
+          <t>Silver Ridge</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 2 bays</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1255,22 +1254,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DS-080</t>
+          <t>DS-115</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Willow Creek</t>
+          <t>Crow Junction</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 3 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1287,12 +1286,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DS-001</t>
+          <t>DS-045</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Basswood Creek</t>
+          <t>Rock Hill</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1302,7 +1301,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1319,22 +1318,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DS-026</t>
+          <t>DS-108</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hemlock Lake</t>
+          <t>Whitefield</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (2 feeder bays)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1351,12 +1350,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DS-020</t>
+          <t>DS-035</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poplarmount</t>
+          <t>Clearton</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1366,7 +1365,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 7 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1383,22 +1382,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DS-126</t>
+          <t>DS-029</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cedar Creek</t>
+          <t>Bear River</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1415,22 +1414,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DS-124</t>
+          <t>DS-022</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pine Junction</t>
+          <t>Wolfford</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 6 bays</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1447,22 +1446,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DS-011</t>
+          <t>TS-090</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Beech Landing</t>
+          <t>Fox Mills</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (7 feeder bays)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1479,22 +1478,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DS-027</t>
+          <t>DS-019</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Aspen Point</t>
+          <t>Glen Bay</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 4 bays</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1511,22 +1510,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DS-006</t>
+          <t>DS-068</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cedar Ridge</t>
+          <t>Iron Corners</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 3 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1543,12 +1542,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DS-077</t>
+          <t>DS-036</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Larch Mills</t>
+          <t>Whitedale</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1558,7 +1557,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (8 bays)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1575,22 +1574,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DS-097</t>
+          <t>DS-139</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Juniper Crossing</t>
+          <t>Birch Landing</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 8 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1607,22 +1606,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DS-105</t>
+          <t>TS-039</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Elm Bay</t>
+          <t>Deerwood</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 1 bays</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1639,12 +1638,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DS-119</t>
+          <t>DS-131</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Basswoodbrook</t>
+          <t>Springwood</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1654,7 +1653,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 5 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1671,22 +1670,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DS-134</t>
+          <t>DS-038</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Juniper Hill</t>
+          <t>Whitemount</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1703,22 +1702,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DS-043</t>
+          <t>DS-126</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Willow Mills</t>
+          <t>Long Falls</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (7 bays)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1735,12 +1734,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DS-073</t>
+          <t>DS-087</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tamarackbrook</t>
+          <t>Wolf River</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1750,7 +1749,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 3 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1767,22 +1766,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DS-042</t>
+          <t>DS-084</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hickory Hill</t>
+          <t>Mill Landing</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 3 bays</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1799,22 +1798,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DS-098</t>
+          <t>DS-067</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poplar Crossing</t>
+          <t>Hawk Hill</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (6 feeder bays)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1831,22 +1830,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DS-072</t>
+          <t>DS-020</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Elm Station</t>
+          <t>Heronwood</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 7 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1863,12 +1862,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DS-039</t>
+          <t>DS-011</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oakdale</t>
+          <t>Port Landing</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1878,7 +1877,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 7 bays</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1895,22 +1894,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DS-012</t>
+          <t>DS-021</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Birch Landing</t>
+          <t>Rock Point</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 1 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1927,22 +1926,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DS-117</t>
+          <t>DS-082</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poplar Junction</t>
+          <t>Wolf Landing</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 7 bays</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1959,12 +1958,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DS-086</t>
+          <t>DS-026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Beech Falls</t>
+          <t>Hawk Junction</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1974,7 +1973,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (7) and RTU</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1991,22 +1990,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DS-069</t>
+          <t>DS-140</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Birchbrook</t>
+          <t>Elmfield</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 6 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2023,22 +2022,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DS-038</t>
+          <t>DS-114</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Beech Mills</t>
+          <t>Glenhurst</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (9) and RTU</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2055,22 +2054,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DS-118</t>
+          <t>DS-061</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Beech Ridge</t>
+          <t>Spring River</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2087,22 +2086,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DS-034</t>
+          <t>DS-062</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Birch Falls</t>
+          <t>Oakton</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (7) and RTU</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2119,12 +2118,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DS-113</t>
+          <t>TS-081</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Basswoodfield</t>
+          <t>Rockwood</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2134,7 +2133,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (4 bays)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2151,22 +2150,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DS-130</t>
+          <t>DS-010</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Larchmount</t>
+          <t>Hawk Bay</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (5 feeder bays)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2183,22 +2182,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DS-052</t>
+          <t>DS-109</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hemlock Crossing</t>
+          <t>Fernwood</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 5 bays</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2215,22 +2214,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DS-108</t>
+          <t>DS-107</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tamarackdale</t>
+          <t>Long Ridge</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 7 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2247,22 +2246,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DS-078</t>
+          <t>DS-116</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hemlock Station</t>
+          <t>Rockmount</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (6) and RTU</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2279,12 +2278,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DS-066</t>
+          <t>DS-137</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Aspen Bay</t>
+          <t>Bear Landing</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2294,7 +2293,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (5 feeder bays)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2311,22 +2310,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DS-087</t>
+          <t>DS-117</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Elm Crossing</t>
+          <t>Willowhurst</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 9 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2343,22 +2342,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DS-057</t>
+          <t>DS-112</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tamarack Corners</t>
+          <t>Sandfield</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 2 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2375,12 +2374,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DS-003</t>
+          <t>DS-047</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tamarack Mills</t>
+          <t>Cedar Ridge</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2390,7 +2389,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (7 feeder bays)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2407,12 +2406,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DS-079</t>
+          <t>DS-070</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cedar Bay</t>
+          <t>Moss Creek</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2422,7 +2421,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (6 bays)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2439,22 +2438,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TS-102</t>
+          <t>DS-095</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>Ashhurst</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 6 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2471,12 +2470,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DS-041</t>
+          <t>DS-032</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sumac Crossing</t>
+          <t>Spring Corners</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2486,7 +2485,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (8 feeder bays)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2503,22 +2502,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DS-023</t>
+          <t>DS-124</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sprucewood</t>
+          <t>Cedar Mills</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (8 feeder bays)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2535,22 +2534,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DS-084</t>
+          <t>DS-135</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Larch Point</t>
+          <t>Fern Point</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (5 feeder bays)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2567,22 +2566,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DS-060</t>
+          <t>DS-007</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Juniper Corners</t>
+          <t>Stone Bridge</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (4 bays)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2599,22 +2598,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DS-045</t>
+          <t>DS-111</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Maple Mills</t>
+          <t>Cedar Bridge</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 8 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2631,12 +2630,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DS-054</t>
+          <t>DS-125</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hemlockbrook</t>
+          <t>Glenfield</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2646,7 +2645,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (7) and RTU</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2663,12 +2662,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TS-013</t>
+          <t>DS-043</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tamarack Point</t>
+          <t>Moss Road</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2678,7 +2677,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (2 bays)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2695,22 +2694,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DS-125</t>
+          <t>DS-071</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Basswoodwood</t>
+          <t>Sugarford</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 3 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2727,12 +2726,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DS-131</t>
+          <t>DS-041</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Larchfield</t>
+          <t>Brant Ridge</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2742,7 +2741,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (7 bays)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2759,22 +2758,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DS-032</t>
+          <t>DS-096</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Willow Lake</t>
+          <t>Iron Point</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 5 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2791,22 +2790,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DS-062</t>
+          <t>DS-094</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Elm Point</t>
+          <t>Willowwood</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (3 feeder bays)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2823,12 +2822,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DS-016</t>
+          <t>DS-004</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ash Point</t>
+          <t>Otter Landing</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2838,7 +2837,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (3) and RTU</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2855,22 +2854,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DS-093</t>
+          <t>DS-101</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oak Corners</t>
+          <t>Silverford</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 4 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2887,12 +2886,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DS-099</t>
+          <t>DS-050</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tamarack Ridge</t>
+          <t>Maplebrook</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2902,7 +2901,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (4 feeder bays)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2919,22 +2918,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TS-101</t>
+          <t>TS-100</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ash Lake</t>
+          <t>Silver Falls</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2951,12 +2950,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DS-128</t>
+          <t>DS-063</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pine Landing</t>
+          <t>Heron Falls</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2966,7 +2965,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (1 feeder bays)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -2983,12 +2982,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DS-009</t>
+          <t>DS-030</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Basswood Landing</t>
+          <t>Millbrook</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2998,7 +2997,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (5 bays)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3015,12 +3014,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DS-137</t>
+          <t>DS-027</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Maplewood</t>
+          <t>North Hill</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3030,7 +3029,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (9 feeder bays)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3047,22 +3046,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DS-061</t>
+          <t>DS-005</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hemlockfield</t>
+          <t>Silver River</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 8 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3079,22 +3078,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DS-115</t>
+          <t>DS-059</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oak Lake</t>
+          <t>Clear Point</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 2 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3111,12 +3110,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DS-082</t>
+          <t>TS-098</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Alder Mills</t>
+          <t>Redwood</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3126,7 +3125,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (6 feeder bays)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3143,12 +3142,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DS-075</t>
+          <t>DS-053</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oak Mills</t>
+          <t>Hawk Mills</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3158,7 +3157,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 3 bays</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3175,22 +3174,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DS-005</t>
+          <t>DS-018</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Maplebrook</t>
+          <t>Sandville</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 2 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3207,22 +3206,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DS-116</t>
+          <t>DS-009</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poplar Point</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (7 bays)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3239,22 +3238,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DS-094</t>
+          <t>TS-055</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pine Ridge</t>
+          <t>High Falls</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 8 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3271,22 +3270,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DS-129</t>
+          <t>DS-056</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Elmfield</t>
+          <t>Crowton</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (8 bays)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3303,12 +3302,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DS-141</t>
+          <t>DS-060</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hickory Lake</t>
+          <t>Otterville</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3318,7 +3317,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 2 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3335,22 +3334,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DS-029</t>
+          <t>DS-057</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pine Station</t>
+          <t>Fern River</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 5 bays</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3367,12 +3366,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DS-047</t>
+          <t>DS-003</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hickory Ridge</t>
+          <t>Grey Mills</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3382,7 +3381,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (4 feeder bays)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3399,22 +3398,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DS-107</t>
+          <t>DS-015</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Maple Crossing</t>
+          <t>Birch Bay</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 8 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3431,22 +3430,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DS-025</t>
+          <t>DS-089</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Beech Junction</t>
+          <t>Greyford</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (8 feeder bays)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3463,22 +3462,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DS-083</t>
+          <t>DS-121</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sumac Hill</t>
+          <t>Otterdale</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (3) and RTU</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3495,22 +3494,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DS-056</t>
+          <t>DS-031</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Oak Point</t>
+          <t>Oak Falls</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (3) and RTU</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3527,22 +3526,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DS-030</t>
+          <t>DS-129</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Alder Junction</t>
+          <t>Lake Mills</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 1 bays</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3559,22 +3558,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DS-002</t>
+          <t>DS-013</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tamarack Junction</t>
+          <t>Springbrook</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 2 bays</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3591,22 +3590,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DS-048</t>
+          <t>DS-076</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Maple Lake</t>
+          <t>Iron Junction</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (5 bays)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3623,22 +3622,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DS-004</t>
+          <t>DS-065</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Elmbrook</t>
+          <t>Sugar River</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (6 feeder bays)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3655,12 +3654,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DS-111</t>
+          <t>DS-079</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hemlock Falls</t>
+          <t>Portford</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3670,7 +3669,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (7) and RTU</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3687,12 +3686,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DS-050</t>
+          <t>DS-132</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Birch Creek</t>
+          <t>Oakdale</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3702,7 +3701,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 5 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3719,22 +3718,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DS-142</t>
+          <t>TS-088</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Pinebrook</t>
+          <t>Otterton</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (8) and RTU</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3751,12 +3750,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DS-036</t>
+          <t>DS-092</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spruce Lake</t>
+          <t>Fern Mills</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3766,7 +3765,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (5 feeder bays)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3779,12 +3778,12 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DS-008</t>
+          <t>DS-023</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cedar Station</t>
+          <t>Grey Bridge</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3794,7 +3793,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (8 feeder bays)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3807,22 +3806,22 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DS-010</t>
+          <t>DS-040</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tamarack Hill</t>
+          <t>Northbrook</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 8 bays</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3835,12 +3834,12 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DS-035</t>
+          <t>DS-073</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tamarack Lake</t>
+          <t>Mapledale</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3850,7 +3849,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 9 bays</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3863,22 +3862,22 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DS-049</t>
+          <t>DS-086</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Willow Bay</t>
+          <t>Greywood</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 6 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3891,22 +3890,22 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DS-063</t>
+          <t>DS-091</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Oakbrook</t>
+          <t>Port Mills</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 6 bays</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3919,12 +3918,12 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DS-074</t>
+          <t>DS-093</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hickory Junction</t>
+          <t>Rock Landing</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3934,7 +3933,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 3 bays</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -3947,22 +3946,22 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DS-127</t>
+          <t>DS-123</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Beech Lake</t>
+          <t>Bearton</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (8) and RTU</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -3975,22 +3974,22 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TS-064</t>
+          <t>DS-141</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cedarbrook</t>
+          <t>Crow Mills</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (2) and RTU</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4003,22 +4002,22 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TS-123</t>
+          <t>TS-085</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Willow Point</t>
+          <t>Mosshurst</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (1 bays)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4096,22 +4095,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DS-065</t>
+          <t>DS-046</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Maple Junction</t>
+          <t>Hawkford</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (3) and RTU</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4128,12 +4127,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DS-135</t>
+          <t>DS-054</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aspen Creek</t>
+          <t>Long River</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4143,7 +4142,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (4 feeder bays)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4160,22 +4159,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TS-103</t>
+          <t>DS-120</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Elm Mills</t>
+          <t>Lakewood</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 3 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4192,12 +4191,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DS-055</t>
+          <t>DS-127</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ash Station</t>
+          <t>Kingsmount</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4207,7 +4206,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 4 bays</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4224,27 +4223,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DS-096</t>
+          <t>DS-080</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poplar Bay</t>
+          <t>Spring Ridge</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (6) and RTU</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Feb 2027</t>
+          <t>Mar 2027</t>
         </is>
       </c>
     </row>
@@ -4256,27 +4255,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TS-044</t>
+          <t>TS-025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oak Station</t>
+          <t>Brant Falls</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (6 feeder bays)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>Apr 2027</t>
         </is>
       </c>
     </row>
@@ -4288,12 +4287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DS-031</t>
+          <t>TS-058</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Juniper Lake</t>
+          <t>Elm Point</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4303,12 +4302,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (1 bays)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>May 2027</t>
         </is>
       </c>
     </row>
@@ -4320,22 +4319,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DS-121</t>
+          <t>DS-119</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alder Landing</t>
+          <t>Cedar Junction</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (1 bays)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4352,12 +4351,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DS-112</t>
+          <t>DS-014</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alder Creek</t>
+          <t>Cedarbrook</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4367,7 +4366,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (2 feeder bays)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4384,22 +4383,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DS-020</t>
+          <t>DS-028</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poplarmount</t>
+          <t>Silver Ridge</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 2 bays</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4416,27 +4415,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DS-095</t>
+          <t>DS-033</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sumac Creek</t>
+          <t>Elmdale</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (4) and RTU</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aug 2027</t>
+          <t>Sep 2027</t>
         </is>
       </c>
     </row>
@@ -4448,22 +4447,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DS-090</t>
+          <t>DS-134</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oak Hill</t>
+          <t>Mossfield</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 2 bays</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4480,12 +4479,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DS-017</t>
+          <t>DS-016</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Birch Mills</t>
+          <t>Long Road</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4495,12 +4494,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 2 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
+          <t>Jan 2028</t>
         </is>
       </c>
     </row>
@@ -4512,27 +4511,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DS-021</t>
+          <t>DS-002</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sumac Mills</t>
+          <t>West River</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (5) and RTU</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dec 2027</t>
+          <t>Feb 2028</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4543,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DS-046</t>
+          <t>DS-064</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Willow Falls</t>
+          <t>Kettle Bridge</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4559,12 +4558,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (5) and RTU</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dec 2027</t>
+          <t>Mar 2028</t>
         </is>
       </c>
     </row>
@@ -4576,12 +4575,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DS-059</t>
+          <t>DS-139</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spruce Ridge</t>
+          <t>Birch Landing</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4591,12 +4590,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 8 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>Mar 2028</t>
         </is>
       </c>
     </row>
@@ -4608,12 +4607,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DS-022</t>
+          <t>DS-038</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ashfield</t>
+          <t>Whitemount</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4623,7 +4622,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4640,27 +4639,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DS-091</t>
+          <t>TS-110</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pine Lake</t>
+          <t>Red Creek</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (7) and RTU</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>May 2028</t>
+          <t>Apr 2028</t>
         </is>
       </c>
     </row>
@@ -4677,22 +4676,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spruce Creek</t>
+          <t>Willow Bridge</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (9 feeder bays)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jun 2028</t>
+          <t>May 2028</t>
         </is>
       </c>
     </row>
@@ -4704,27 +4703,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DS-124</t>
+          <t>DS-069</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pine Junction</t>
+          <t>Sand Landing</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (6 feeder bays)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jul 2028</t>
+          <t>Jun 2028</t>
         </is>
       </c>
     </row>
@@ -4736,12 +4735,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DS-132</t>
+          <t>DS-122</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pine Crossing</t>
+          <t>Ash Bridge</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4751,7 +4750,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 8 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4768,12 +4767,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DS-006</t>
+          <t>DS-075</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cedar Ridge</t>
+          <t>Ash Creek</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4783,12 +4782,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (1) and RTU</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aug 2028</t>
+          <t>Sep 2028</t>
         </is>
       </c>
     </row>
@@ -4800,12 +4799,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DS-071</t>
+          <t>DS-104</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sumacwood</t>
+          <t>Stone Mills</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4815,12 +4814,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 6 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sep 2028</t>
+          <t>Nov 2028</t>
         </is>
       </c>
     </row>
@@ -4832,12 +4831,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DS-077</t>
+          <t>TS-138</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Larch Mills</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4847,12 +4846,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 8 bays</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sep 2028</t>
+          <t>Dec 2028</t>
         </is>
       </c>
     </row>
@@ -4864,27 +4863,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DS-027</t>
+          <t>DS-001</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Aspen Point</t>
+          <t>Cedar Road</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oct 2028</t>
+          <t>Feb 2029</t>
         </is>
       </c>
     </row>
@@ -4896,27 +4895,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DS-014</t>
+          <t>DS-115</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oak Landing</t>
+          <t>Crow Junction</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 3 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nov 2028</t>
+          <t>Feb 2029</t>
         </is>
       </c>
     </row>
@@ -4928,12 +4927,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DS-114</t>
+          <t>DS-045</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tamarack Bay</t>
+          <t>Rock Hill</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4943,12 +4942,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Mar 2029</t>
         </is>
       </c>
     </row>
@@ -4960,27 +4959,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DS-136</t>
+          <t>DS-108</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Beech Creek</t>
+          <t>Whitefield</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (2 feeder bays)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Apr 2029</t>
         </is>
       </c>
     </row>
@@ -4992,12 +4991,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DS-080</t>
+          <t>DS-035</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Willow Creek</t>
+          <t>Clearton</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5007,12 +5006,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 7 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Feb 2029</t>
+          <t>May 2029</t>
         </is>
       </c>
     </row>
@@ -5024,27 +5023,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DS-001</t>
+          <t>DS-029</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Basswood Creek</t>
+          <t>Bear River</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mar 2029</t>
+          <t>Jun 2029</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5055,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DS-026</t>
+          <t>DS-022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hemlock Lake</t>
+          <t>Wolfford</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5071,12 +5070,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 6 bays</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Apr 2029</t>
+          <t>Jul 2029</t>
         </is>
       </c>
     </row>
@@ -5088,27 +5087,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DS-073</t>
+          <t>DS-061</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tamarackbrook</t>
+          <t>Spring River</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jun 2029</t>
+          <t>Jul 2029</t>
         </is>
       </c>
     </row>
@@ -5120,27 +5119,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DS-126</t>
+          <t>TS-090</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cedar Creek</t>
+          <t>Fox Mills</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (7 feeder bays)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jun 2029</t>
+          <t>Aug 2029</t>
         </is>
       </c>
     </row>
@@ -5152,27 +5151,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DS-011</t>
+          <t>DS-019</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Beech Landing</t>
+          <t>Glen Bay</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 4 bays</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aug 2029</t>
+          <t>Sep 2029</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5183,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DS-117</t>
+          <t>DS-107</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poplar Junction</t>
+          <t>Long Ridge</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5199,12 +5198,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 7 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aug 2029</t>
+          <t>Sep 2029</t>
         </is>
       </c>
     </row>
@@ -5216,27 +5215,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DS-097</t>
+          <t>DS-068</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Juniper Crossing</t>
+          <t>Iron Corners</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 3 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dec 2029</t>
+          <t>Oct 2029</t>
         </is>
       </c>
     </row>
@@ -5248,27 +5247,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DS-105</t>
+          <t>DS-036</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Elm Bay</t>
+          <t>Whitedale</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (8 bays)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jan 2030</t>
+          <t>Nov 2029</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5279,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DS-119</t>
+          <t>DS-128</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Basswoodbrook</t>
+          <t>Rock Bay</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5295,12 +5294,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Feb 2030</t>
+          <t>Nov 2029</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5311,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DS-134</t>
+          <t>DS-137</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Juniper Hill</t>
+          <t>Bear Landing</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5327,12 +5326,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (5 feeder bays)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mar 2030</t>
+          <t>Nov 2029</t>
         </is>
       </c>
     </row>
@@ -5344,12 +5343,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DS-138</t>
+          <t>TS-039</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ash Bay</t>
+          <t>Deerwood</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5359,12 +5358,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 1 bays</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mar 2030</t>
+          <t>Jan 2030</t>
         </is>
       </c>
     </row>
@@ -5376,12 +5375,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DS-043</t>
+          <t>DS-062</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Willow Mills</t>
+          <t>Oakton</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5391,12 +5390,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (7) and RTU</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Apr 2030</t>
+          <t>Feb 2030</t>
         </is>
       </c>
     </row>
@@ -5408,27 +5407,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DS-042</t>
+          <t>DS-131</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hickory Hill</t>
+          <t>Springwood</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 5 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jun 2030</t>
+          <t>Feb 2030</t>
         </is>
       </c>
     </row>
@@ -5440,27 +5439,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DS-098</t>
+          <t>DS-126</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poplar Crossing</t>
+          <t>Long Falls</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (7 bays)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jul 2030</t>
+          <t>Apr 2030</t>
         </is>
       </c>
     </row>
@@ -5472,12 +5471,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DS-072</t>
+          <t>DS-084</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Elm Station</t>
+          <t>Mill Landing</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5487,12 +5486,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 3 bays</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sep 2030</t>
+          <t>Jun 2030</t>
         </is>
       </c>
     </row>
@@ -5504,27 +5503,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DS-039</t>
+          <t>DS-135</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oakdale</t>
+          <t>Fern Point</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (5 feeder bays)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oct 2030</t>
+          <t>Jun 2030</t>
         </is>
       </c>
     </row>
@@ -5536,27 +5535,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DS-012</t>
+          <t>DS-067</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Birch Landing</t>
+          <t>Hawk Hill</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (6 feeder bays)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nov 2030</t>
+          <t>Jul 2030</t>
         </is>
       </c>
     </row>
@@ -5568,27 +5567,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DS-086</t>
+          <t>DS-020</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Beech Falls</t>
+          <t>Heronwood</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 7 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Jan 2031</t>
+          <t>Sep 2030</t>
         </is>
       </c>
     </row>
@@ -5600,27 +5599,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DS-130</t>
+          <t>DS-011</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Larchmount</t>
+          <t>Port Landing</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 7 bays</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jan 2031</t>
+          <t>Oct 2030</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5631,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DS-078</t>
+          <t>DS-021</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hemlock Station</t>
+          <t>Rock Point</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5647,12 +5646,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 1 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Feb 2031</t>
+          <t>Nov 2030</t>
         </is>
       </c>
     </row>
@@ -5664,27 +5663,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DS-034</t>
+          <t>DS-026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Birch Falls</t>
+          <t>Hawk Junction</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (7) and RTU</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>May 2031</t>
+          <t>Jan 2031</t>
         </is>
       </c>
     </row>
@@ -5696,27 +5695,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DS-113</t>
+          <t>DS-140</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Basswoodfield</t>
+          <t>Elmfield</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 6 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jun 2031</t>
+          <t>Feb 2031</t>
         </is>
       </c>
     </row>
@@ -5728,27 +5727,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DS-052</t>
+          <t>DS-114</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hemlock Crossing</t>
+          <t>Glenhurst</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (9) and RTU</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aug 2031</t>
+          <t>Mar 2031</t>
         </is>
       </c>
     </row>
@@ -5760,27 +5759,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DS-108</t>
+          <t>DS-050</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tamarackdale</t>
+          <t>Maplebrook</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (4 feeder bays)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sep 2031</t>
+          <t>May 2031</t>
         </is>
       </c>
     </row>
@@ -5792,12 +5791,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DS-137</t>
+          <t>DS-010</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Maplewood</t>
+          <t>Hawk Bay</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5807,12 +5806,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (5 feeder bays)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Oct 2031</t>
+          <t>Jul 2031</t>
         </is>
       </c>
     </row>
@@ -5824,27 +5823,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DS-016</t>
+          <t>DS-032</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ash Point</t>
+          <t>Spring Corners</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (8 feeder bays)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nov 2031</t>
+          <t>Oct 2031</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5855,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DS-066</t>
+          <t>DS-116</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Aspen Bay</t>
+          <t>Rockmount</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5871,12 +5870,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (6) and RTU</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nov 2031</t>
+          <t>Oct 2031</t>
         </is>
       </c>
     </row>
@@ -5888,22 +5887,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DS-087</t>
+          <t>DS-117</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Elm Crossing</t>
+          <t>Willowhurst</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 9 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5920,22 +5919,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DS-057</t>
+          <t>DS-112</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tamarack Corners</t>
+          <t>Sandfield</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 2 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5952,12 +5951,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DS-003</t>
+          <t>DS-047</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tamarack Mills</t>
+          <t>Cedar Ridge</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5967,7 +5966,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (7 feeder bays)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5984,12 +5983,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DS-079</t>
+          <t>DS-070</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cedar Bay</t>
+          <t>Moss Creek</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5999,7 +5998,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (6 bays)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6016,22 +6015,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DS-032</t>
+          <t>DS-095</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Willow Lake</t>
+          <t>Ashhurst</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 6 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6048,12 +6047,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TS-102</t>
+          <t>DS-109</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pine Hill</t>
+          <t>Fernwood</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6063,12 +6062,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 5 bays</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Apr 2032</t>
+          <t>Jul 2032</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6079,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DS-041</t>
+          <t>DS-124</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sumac Crossing</t>
+          <t>Cedar Mills</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6095,12 +6094,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (8 feeder bays)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jun 2032</t>
+          <t>Jul 2032</t>
         </is>
       </c>
     </row>
@@ -6112,27 +6111,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DS-023</t>
+          <t>TS-055</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sprucewood</t>
+          <t>High Falls</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 8 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jul 2032</t>
+          <t>Aug 2032</t>
         </is>
       </c>
     </row>
@@ -6144,12 +6143,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DS-038</t>
+          <t>DS-007</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Beech Mills</t>
+          <t>Stone Bridge</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6159,12 +6158,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (4 bays)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jul 2032</t>
+          <t>Sep 2032</t>
         </is>
       </c>
     </row>
@@ -6176,27 +6175,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DS-084</t>
+          <t>DS-087</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Larch Point</t>
+          <t>Wolf River</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 3 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Aug 2032</t>
+          <t>Sep 2032</t>
         </is>
       </c>
     </row>
@@ -6208,27 +6207,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DS-060</t>
+          <t>DS-111</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Juniper Corners</t>
+          <t>Cedar Bridge</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 8 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sep 2032</t>
+          <t>Oct 2032</t>
         </is>
       </c>
     </row>
@@ -6240,27 +6239,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DS-045</t>
+          <t>DS-125</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Maple Mills</t>
+          <t>Glenfield</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (7) and RTU</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oct 2032</t>
+          <t>Nov 2032</t>
         </is>
       </c>
     </row>
@@ -6272,27 +6271,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DS-054</t>
+          <t>DS-043</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hemlockbrook</t>
+          <t>Moss Road</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (2 bays)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nov 2032</t>
+          <t>Dec 2032</t>
         </is>
       </c>
     </row>
@@ -6304,27 +6303,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DS-061</t>
+          <t>DS-082</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hemlockfield</t>
+          <t>Wolf Landing</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 7 bays</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nov 2032</t>
+          <t>Dec 2032</t>
         </is>
       </c>
     </row>
@@ -6336,27 +6335,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TS-013</t>
+          <t>DS-071</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tamarack Point</t>
+          <t>Sugarford</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 3 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dec 2032</t>
+          <t>Jan 2033</t>
         </is>
       </c>
     </row>
@@ -6368,12 +6367,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DS-125</t>
+          <t>DS-041</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Basswoodwood</t>
+          <t>Brant Ridge</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6383,12 +6382,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (7 bays)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Jan 2033</t>
+          <t>Feb 2033</t>
         </is>
       </c>
     </row>
@@ -6400,12 +6399,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DS-131</t>
+          <t>DS-053</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Larchfield</t>
+          <t>Hawk Mills</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6415,7 +6414,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 3 bays</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6432,12 +6431,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TS-101</t>
+          <t>DS-096</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ash Lake</t>
+          <t>Iron Point</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6447,12 +6446,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 5 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Feb 2033</t>
+          <t>Mar 2033</t>
         </is>
       </c>
     </row>
@@ -6464,22 +6463,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DS-062</t>
+          <t>DS-094</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Elm Point</t>
+          <t>Willowwood</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (3 feeder bays)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6496,12 +6495,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DS-093</t>
+          <t>TS-081</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oak Corners</t>
+          <t>Rockwood</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6511,12 +6510,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (4 bays)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Jun 2033</t>
+          <t>Apr 2033</t>
         </is>
       </c>
     </row>
@@ -6528,27 +6527,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DS-069</t>
+          <t>DS-004</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Birchbrook</t>
+          <t>Otter Landing</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (3) and RTU</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jul 2033</t>
+          <t>May 2033</t>
         </is>
       </c>
     </row>
@@ -6560,27 +6559,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DS-099</t>
+          <t>DS-101</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tamarack Ridge</t>
+          <t>Silverford</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 4 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jul 2033</t>
+          <t>Jun 2033</t>
         </is>
       </c>
     </row>
@@ -6592,12 +6591,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DS-118</t>
+          <t>TS-100</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Beech Ridge</t>
+          <t>Silver Falls</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6607,7 +6606,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 4 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6624,12 +6623,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DS-128</t>
+          <t>DS-063</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pine Landing</t>
+          <t>Heron Falls</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6639,7 +6638,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (1 feeder bays)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6656,12 +6655,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DS-009</t>
+          <t>DS-030</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Basswood Landing</t>
+          <t>Millbrook</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6671,7 +6670,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (5 bays)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6688,27 +6687,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DS-115</t>
+          <t>DS-027</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oak Lake</t>
+          <t>North Hill</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (9 feeder bays)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jan 2034</t>
+          <t>Nov 2033</t>
         </is>
       </c>
     </row>
@@ -6720,27 +6719,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DS-082</t>
+          <t>DS-005</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Alder Mills</t>
+          <t>Silver River</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 8 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Feb 2034</t>
+          <t>Dec 2033</t>
         </is>
       </c>
     </row>
@@ -6752,12 +6751,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DS-075</t>
+          <t>DS-059</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oak Mills</t>
+          <t>Clear Point</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6767,12 +6766,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 2 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Apr 2034</t>
+          <t>Jan 2034</t>
         </is>
       </c>
     </row>
@@ -6784,27 +6783,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DS-005</t>
+          <t>TS-098</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Maplebrook</t>
+          <t>Redwood</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (6 feeder bays)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>May 2034</t>
+          <t>Feb 2034</t>
         </is>
       </c>
     </row>
@@ -6816,27 +6815,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DS-116</t>
+          <t>DS-018</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poplar Point</t>
+          <t>Sandville</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder protection upgrade, 2 bays, IEC 61850 station bus</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Jun 2034</t>
+          <t>May 2034</t>
         </is>
       </c>
     </row>
@@ -6848,27 +6847,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DS-094</t>
+          <t>DS-009</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pine Ridge</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (7 bays)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Jul 2034</t>
+          <t>Jun 2034</t>
         </is>
       </c>
     </row>
@@ -6880,22 +6879,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DS-129</t>
+          <t>DS-056</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Elmfield</t>
+          <t>Crowton</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (8 bays)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6912,12 +6911,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DS-141</t>
+          <t>DS-060</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hickory Lake</t>
+          <t>Otterville</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6927,7 +6926,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 2 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6944,27 +6943,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DS-047</t>
+          <t>DS-057</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hickory Ridge</t>
+          <t>Fern River</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 5 bays</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nov 2034</t>
+          <t>Oct 2034</t>
         </is>
       </c>
     </row>
@@ -6976,27 +6975,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DS-107</t>
+          <t>DS-003</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Maple Crossing</t>
+          <t>Grey Mills</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (4 feeder bays)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dec 2034</t>
+          <t>Nov 2034</t>
         </is>
       </c>
     </row>
@@ -7008,22 +7007,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DS-025</t>
+          <t>DS-089</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Beech Junction</t>
+          <t>Greyford</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (8 feeder bays)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7040,22 +7039,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DS-083</t>
+          <t>DS-121</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sumac Hill</t>
+          <t>Otterdale</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (3) and RTU</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7072,22 +7071,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DS-056</t>
+          <t>DS-031</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Oak Point</t>
+          <t>Oak Falls</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (3) and RTU</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7104,22 +7103,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DS-030</t>
+          <t>DS-129</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Alder Junction</t>
+          <t>Lake Mills</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 1 bays</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7136,22 +7135,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DS-002</t>
+          <t>DS-013</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tamarack Junction</t>
+          <t>Springbrook</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 2 bays</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7168,22 +7167,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DS-048</t>
+          <t>DS-076</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Maple Lake</t>
+          <t>Iron Junction</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (5 bays)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7200,22 +7199,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DS-004</t>
+          <t>DS-065</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Elmbrook</t>
+          <t>Sugar River</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (6 feeder bays)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7232,12 +7231,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DS-111</t>
+          <t>DS-079</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hemlock Falls</t>
+          <t>Portford</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -7247,7 +7246,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (7) and RTU</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -7264,12 +7263,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DS-050</t>
+          <t>DS-132</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Birch Creek</t>
+          <t>Oakdale</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7279,7 +7278,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 5 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -7296,22 +7295,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DS-142</t>
+          <t>TS-088</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pinebrook</t>
+          <t>Otterton</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (8) and RTU</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -7328,12 +7327,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DS-036</t>
+          <t>DS-092</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spruce Lake</t>
+          <t>Fern Mills</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -7343,7 +7342,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (5 feeder bays)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7360,12 +7359,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DS-029</t>
+          <t>DS-015</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pine Station</t>
+          <t>Birch Bay</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7375,12 +7374,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 8 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Jul 2036</t>
+          <t>Apr 2037</t>
         </is>
       </c>
     </row>
@@ -7388,12 +7387,12 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DS-008</t>
+          <t>DS-023</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cedar Station</t>
+          <t>Grey Bridge</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -7403,7 +7402,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Protection and control panel replacement (8 feeder bays)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -7416,22 +7415,22 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DS-010</t>
+          <t>DS-040</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tamarack Hill</t>
+          <t>Northbrook</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 8 bays</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7444,12 +7443,12 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DS-035</t>
+          <t>DS-073</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tamarack Lake</t>
+          <t>Mapledale</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7459,7 +7458,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 9 bays</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -7472,22 +7471,22 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DS-049</t>
+          <t>DS-086</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Willow Bay</t>
+          <t>Greywood</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Feeder relay replacement, 6 bays, with panel rewiring</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7500,22 +7499,22 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DS-063</t>
+          <t>DS-091</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Oakbrook</t>
+          <t>Port Mills</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 6 bays</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7528,12 +7527,12 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DS-074</t>
+          <t>DS-093</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hickory Junction</t>
+          <t>Rock Landing</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7543,7 +7542,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace feeder protection, 3 bays</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7556,22 +7555,22 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DS-127</t>
+          <t>DS-123</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Beech Lake</t>
+          <t>Bearton</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (8) and RTU</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7584,22 +7583,22 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TS-064</t>
+          <t>DS-141</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cedarbrook</t>
+          <t>Crow Mills</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>Replace VPR-340 feeder relays (2) and RTU</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7612,22 +7611,22 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TS-123</t>
+          <t>TS-085</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Willow Point</t>
+          <t>Mosshurst</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Replace feeder protection (VPR-340) and panel wiring</t>
+          <t>P&amp;C rebuild with new control building (1 bays)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7677,7 +7676,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>The 2026 programme defers 18 schemes and brings 5 forward against the 2025 planning version.</t>
+          <t>The 2026 programme defers 16 schemes and brings 7 forward against the 2025 planning version.</t>
         </is>
       </c>
     </row>
